--- a/data/trans_camb/P2C_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 18,88</t>
+          <t>3,97; 19,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,41; 18,64</t>
+          <t>3,5; 19,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-50,95; -25,87</t>
+          <t>-49,95; -25,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 19,62</t>
+          <t>3,91; 18,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 16,5</t>
+          <t>0,05; 15,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,63; -17,39</t>
+          <t>-40,57; -16,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,5; 16,81</t>
+          <t>6,41; 16,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 15,23</t>
+          <t>4,78; 16,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-41,73; -25,73</t>
+          <t>-41,96; -25,23</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 24,77</t>
+          <t>4,53; 25,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,93; 24,07</t>
+          <t>4,01; 25,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-59,31; -33,2</t>
+          <t>-58,41; -33,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,2; 25,85</t>
+          <t>4,62; 24,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 21,82</t>
+          <t>0,08; 20,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,96; -22,02</t>
+          <t>-47,41; -22,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 21,52</t>
+          <t>7,48; 21,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 19,35</t>
+          <t>5,63; 20,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-49,42; -31,7</t>
+          <t>-49,22; -31,75</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,97; 15,6</t>
+          <t>6,21; 16,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 7,22</t>
+          <t>-4,82; 7,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-58,46; -43,3</t>
+          <t>-58,6; -43,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,34; 14,99</t>
+          <t>3,73; 14,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 11,5</t>
+          <t>0,49; 12,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,59; -34,55</t>
+          <t>-48,73; -33,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,02; 13,29</t>
+          <t>6,44; 13,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 7,82</t>
+          <t>-0,57; 8,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-51,49; -41,05</t>
+          <t>-51,56; -40,78</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 19,32</t>
+          <t>7,23; 20,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 8,65</t>
+          <t>-5,49; 9,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,71; -52,35</t>
+          <t>-67,12; -52,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,15; 19,17</t>
+          <t>4,48; 18,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 14,36</t>
+          <t>0,63; 15,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,8; -42,57</t>
+          <t>-57,71; -41,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,14; 16,48</t>
+          <t>7,59; 17,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 9,73</t>
+          <t>-0,66; 9,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-60,71; -49,85</t>
+          <t>-60,71; -49,41</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,16; 35,63</t>
+          <t>16,1; 35,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 19,0</t>
+          <t>-2,12; 18,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-43,49; -23,16</t>
+          <t>-43,22; -22,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,72; 27,03</t>
+          <t>6,88; 26,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 15,91</t>
+          <t>-4,01; 15,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-50,07; -31,92</t>
+          <t>-50,36; -32,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,14; 27,82</t>
+          <t>14,87; 28,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 14,61</t>
+          <t>0,36; 14,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-44,24; -30,6</t>
+          <t>-43,7; -29,38</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,86; 63,13</t>
+          <t>22,6; 61,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 32,21</t>
+          <t>-2,78; 33,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,73; -39,47</t>
+          <t>-61,06; -37,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,77; 44,19</t>
+          <t>9,35; 41,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 25,51</t>
+          <t>-5,28; 24,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,59; -50,03</t>
+          <t>-69,02; -50,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,04; 44,63</t>
+          <t>20,67; 45,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,47; 23,59</t>
+          <t>0,49; 23,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-63,14; -48,55</t>
+          <t>-62,69; -47,72</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,34; 40,12</t>
+          <t>21,64; 40,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-17,66; 2,05</t>
+          <t>-18,03; 2,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-32,83; -15,14</t>
+          <t>-33,01; -14,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,14; 42,93</t>
+          <t>25,55; 43,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 10,54</t>
+          <t>-8,61; 11,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,12; -5,25</t>
+          <t>-24,28; -4,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,01; 38,51</t>
+          <t>26,9; 39,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 3,09</t>
+          <t>-10,1; 3,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-26,49; -13,64</t>
+          <t>-25,98; -12,3</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>41,37; 98,19</t>
+          <t>41,89; 100,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,93; 4,7</t>
+          <t>-35,45; 5,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-65,88; -34,83</t>
+          <t>-66,01; -33,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50,83; 108,68</t>
+          <t>52,51; 116,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 26,41</t>
+          <t>-17,81; 27,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,35; -11,48</t>
+          <t>-50,46; -10,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,48; 93,25</t>
+          <t>54,98; 96,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,33; 7,52</t>
+          <t>-20,47; 8,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-55,39; -31,59</t>
+          <t>-54,76; -29,12</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,35; 24,1</t>
+          <t>16,24; 24,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 7,73</t>
+          <t>-0,84; 7,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-44,79; -35,05</t>
+          <t>-45,04; -35,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,65; 22,76</t>
+          <t>14,95; 22,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,75; 10,92</t>
+          <t>2,19; 11,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-40,41; -30,73</t>
+          <t>-40,16; -30,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,89; 22,53</t>
+          <t>16,84; 22,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 8,52</t>
+          <t>1,9; 8,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-41,11; -34,21</t>
+          <t>-41,31; -34,19</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>22,77; 36,14</t>
+          <t>22,31; 36,13</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 11,5</t>
+          <t>-1,2; 11,88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-63,86; -51,59</t>
+          <t>-63,35; -51,8</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,51; 34,68</t>
+          <t>20,83; 34,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,44; 16,38</t>
+          <t>3,19; 17,39</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-57,37; -45,93</t>
+          <t>-56,98; -45,79</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,7; 33,57</t>
+          <t>23,69; 33,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,68; 12,57</t>
+          <t>2,69; 11,85</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-58,26; -50,45</t>
+          <t>-58,68; -50,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 19,16</t>
+          <t>4,14; 19,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 19,1</t>
+          <t>3,26; 18,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-49,95; -25,98</t>
+          <t>-51,49; -26,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 18,7</t>
+          <t>4,6; 19,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 15,87</t>
+          <t>0,56; 17,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,57; -16,85</t>
+          <t>-40,24; -16,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,41; 16,59</t>
+          <t>6,06; 17,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,78; 16,2</t>
+          <t>5,19; 16,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-41,96; -25,23</t>
+          <t>-42,23; -25,22</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 25,31</t>
+          <t>4,84; 26,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,01; 25,01</t>
+          <t>4,18; 25,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-58,41; -33,15</t>
+          <t>-59,44; -34,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 24,42</t>
+          <t>5,33; 26,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 20,8</t>
+          <t>0,91; 23,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,41; -22,41</t>
+          <t>-47,42; -21,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,48; 21,26</t>
+          <t>7,02; 22,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,63; 20,91</t>
+          <t>6,12; 21,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-49,22; -31,75</t>
+          <t>-49,85; -31,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,21; 16,58</t>
+          <t>5,58; 15,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 7,58</t>
+          <t>-4,44; 7,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-58,6; -43,2</t>
+          <t>-58,59; -43,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 14,77</t>
+          <t>4,0; 15,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 12,05</t>
+          <t>-0,02; 11,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-48,73; -33,13</t>
+          <t>-48,8; -33,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,44; 13,99</t>
+          <t>5,9; 13,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 8,03</t>
+          <t>-0,23; 8,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-51,56; -40,78</t>
+          <t>-51,37; -40,9</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,23; 20,83</t>
+          <t>6,5; 18,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 9,18</t>
+          <t>-5,13; 8,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,12; -52,2</t>
+          <t>-67,19; -52,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 18,9</t>
+          <t>4,96; 20,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 15,46</t>
+          <t>0,06; 14,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,71; -41,34</t>
+          <t>-58,22; -42,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,59; 17,49</t>
+          <t>6,9; 17,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 9,83</t>
+          <t>-0,31; 10,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-60,71; -49,41</t>
+          <t>-60,37; -49,74</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,1; 35,2</t>
+          <t>16,57; 34,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 18,95</t>
+          <t>-1,46; 19,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-43,22; -22,61</t>
+          <t>-42,17; -22,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,88; 26,0</t>
+          <t>8,38; 26,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 15,66</t>
+          <t>-4,76; 15,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-50,36; -32,02</t>
+          <t>-49,62; -31,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,87; 28,29</t>
+          <t>14,91; 27,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 14,71</t>
+          <t>0,01; 13,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-43,7; -29,38</t>
+          <t>-43,71; -30,28</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,6; 61,34</t>
+          <t>23,45; 60,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 33,08</t>
+          <t>-1,85; 33,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,06; -37,7</t>
+          <t>-61,08; -38,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,35; 41,24</t>
+          <t>11,63; 42,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 24,5</t>
+          <t>-6,09; 23,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,02; -50,36</t>
+          <t>-68,39; -49,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,67; 45,92</t>
+          <t>20,79; 44,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,49; 23,71</t>
+          <t>-0,04; 21,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,69; -47,72</t>
+          <t>-62,62; -47,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,64; 40,57</t>
+          <t>22,1; 39,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 2,19</t>
+          <t>-18,0; 2,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-33,01; -14,18</t>
+          <t>-34,01; -14,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,55; 43,62</t>
+          <t>25,67; 44,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 11,08</t>
+          <t>-8,63; 11,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,28; -4,54</t>
+          <t>-23,68; -4,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,9; 39,27</t>
+          <t>26,74; 38,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 3,62</t>
+          <t>-10,58; 3,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-25,98; -12,3</t>
+          <t>-26,63; -12,57</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>41,89; 100,22</t>
+          <t>43,57; 97,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,45; 5,52</t>
+          <t>-35,67; 4,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-66,01; -33,94</t>
+          <t>-65,82; -34,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52,51; 116,49</t>
+          <t>51,06; 115,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 27,32</t>
+          <t>-18,31; 28,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,46; -10,79</t>
+          <t>-49,91; -11,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,98; 96,58</t>
+          <t>54,73; 93,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,47; 8,51</t>
+          <t>-21,44; 7,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-54,76; -29,12</t>
+          <t>-54,87; -29,46</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,24; 24,16</t>
+          <t>16,71; 24,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 7,93</t>
+          <t>-0,83; 8,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-45,04; -35,21</t>
+          <t>-45,23; -35,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,95; 22,75</t>
+          <t>14,87; 23,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,19; 11,4</t>
+          <t>2,38; 11,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-40,16; -30,72</t>
+          <t>-40,55; -31,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,84; 22,39</t>
+          <t>16,88; 22,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,9; 8,06</t>
+          <t>1,87; 7,94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-41,31; -34,19</t>
+          <t>-41,14; -34,49</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>22,31; 36,13</t>
+          <t>23,23; 37,78</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 11,88</t>
+          <t>-1,16; 12,21</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-63,35; -51,8</t>
+          <t>-63,6; -52,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,83; 34,33</t>
+          <t>20,68; 35,26</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,19; 17,39</t>
+          <t>3,41; 16,93</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-56,98; -45,79</t>
+          <t>-57,48; -46,15</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,69; 33,24</t>
+          <t>23,74; 33,12</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,69; 11,85</t>
+          <t>2,65; 11,78</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-58,68; -50,46</t>
+          <t>-58,81; -50,76</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,28</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8,79</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-29,27</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>11,03</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>10,68</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-39,08</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,28</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,79</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-28,87</t>
+          <t>-40,85</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-33,79</t>
+          <t>-35,12</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,14; 19,56</t>
+          <t>4,44; 19,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 18,81</t>
+          <t>1,24; 16,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-51,49; -26,95</t>
+          <t>-41,7; -17,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 19,78</t>
+          <t>3,21; 18,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 17,43</t>
+          <t>3,41; 18,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,24; -16,43</t>
+          <t>-53,03; -27,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,06; 17,21</t>
+          <t>6,5; 16,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,19; 16,35</t>
+          <t>4,09; 15,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-42,23; -25,22</t>
+          <t>-43,48; -27,1</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13,69%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-35,53%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>13,25%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>12,83%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-46,96%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-35,04%</t>
+          <t>-49,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-40,82%</t>
+          <t>-42,42%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 26,21</t>
+          <t>5,2; 25,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 25,01</t>
+          <t>1,46; 21,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-59,44; -34,14</t>
+          <t>-49,24; -22,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 26,18</t>
+          <t>3,66; 24,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 23,32</t>
+          <t>3,93; 24,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,42; -21,32</t>
+          <t>-61,22; -35,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,02; 22,01</t>
+          <t>7,55; 21,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,12; 21,29</t>
+          <t>4,76; 19,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-49,85; -31,11</t>
+          <t>-50,94; -33,57</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,56</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,84</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-41,01</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>10,6</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,19</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-51,27</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,56</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,84</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-41,65</t>
+          <t>-49,62</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-46,22</t>
+          <t>-45,19</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,58; 15,38</t>
+          <t>4,34; 14,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 7,14</t>
+          <t>0,18; 11,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-58,59; -43,39</t>
+          <t>-49,27; -33,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 15,54</t>
+          <t>5,97; 15,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 11,67</t>
+          <t>-5,31; 7,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-48,8; -33,94</t>
+          <t>-57,57; -42,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,9; 13,84</t>
+          <t>6,02; 13,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 8,2</t>
+          <t>-0,41; 7,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-51,37; -40,9</t>
+          <t>-50,67; -40,04</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11,61%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-49,8%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>12,47%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-60,32%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11,61%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-50,58%</t>
+          <t>-58,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-55,24%</t>
+          <t>-54,02%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 18,91</t>
+          <t>5,15; 19,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 8,8</t>
+          <t>0,18; 14,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,19; -52,22</t>
+          <t>-58,6; -41,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 20,06</t>
+          <t>6,76; 19,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 14,8</t>
+          <t>-6,11; 8,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,22; -42,82</t>
+          <t>-65,73; -50,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 17,33</t>
+          <t>7,14; 16,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 10,11</t>
+          <t>-0,43; 9,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-60,37; -49,74</t>
+          <t>-59,88; -48,79</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17,86</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,72</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-39,08</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>26,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>8,49</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-33,04</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17,86</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,72</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-41,25</t>
+          <t>-31,06</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-37,53</t>
+          <t>-35,37</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,57; 34,61</t>
+          <t>8,72; 27,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 19,03</t>
+          <t>-4,89; 15,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-42,17; -22,0</t>
+          <t>-48,1; -29,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,38; 26,09</t>
+          <t>16,16; 35,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 15,04</t>
+          <t>-1,66; 19,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-49,62; -31,69</t>
+          <t>-41,49; -21,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,91; 27,83</t>
+          <t>15,14; 27,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 13,6</t>
+          <t>0,29; 14,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-43,71; -30,28</t>
+          <t>-42,47; -28,69</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>26,04%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8,34%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-56,97%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>40,02%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>13,07%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-50,87%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26,04%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-60,13%</t>
+          <t>-47,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-56,07%</t>
+          <t>-52,85%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,45; 60,55</t>
+          <t>11,77; 44,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 33,39</t>
+          <t>-6,5; 25,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,08; -38,19</t>
+          <t>-65,74; -46,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,63; 42,71</t>
+          <t>22,86; 63,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 23,83</t>
+          <t>-2,36; 32,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,39; -49,91</t>
+          <t>-59,32; -36,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,79; 44,65</t>
+          <t>21,04; 44,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 21,68</t>
+          <t>0,47; 23,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,62; -47,79</t>
+          <t>-60,23; -45,01</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>34,59</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,17</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-14,18</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>31,01</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-8,24</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-23,42</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>34,59</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-15,61</t>
+          <t>-22,21</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-19,39</t>
+          <t>-18,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,1; 39,45</t>
+          <t>25,14; 42,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 2,1</t>
+          <t>-8,92; 10,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-34,01; -14,74</t>
+          <t>-22,59; -4,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,67; 44,33</t>
+          <t>21,34; 40,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 11,08</t>
+          <t>-17,66; 2,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-23,68; -4,52</t>
+          <t>-30,4; -14,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,74; 38,69</t>
+          <t>26,01; 38,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 3,37</t>
+          <t>-11,09; 3,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-26,63; -12,57</t>
+          <t>-24,21; -12,43</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>79,18%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-32,46%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>66,9%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-17,77%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-50,52%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>79,18%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-35,74%</t>
+          <t>-47,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-43,07%</t>
+          <t>-40,04%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>43,57; 97,24</t>
+          <t>50,83; 108,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,67; 4,13</t>
+          <t>-18,76; 26,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-65,82; -34,52</t>
+          <t>-47,15; -10,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51,06; 115,54</t>
+          <t>41,37; 98,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,31; 28,89</t>
+          <t>-34,93; 4,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,91; -11,29</t>
+          <t>-59,79; -33,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,73; 93,66</t>
+          <t>53,48; 93,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,44; 7,94</t>
+          <t>-22,33; 7,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-54,87; -29,46</t>
+          <t>-50,84; -29,82</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>19,08</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6,79</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-34,96</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>20,25</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>3,34</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-39,99</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>19,08</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>6,79</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-35,89</t>
+          <t>-38,71</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-37,82</t>
+          <t>-36,75</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,71; 24,87</t>
+          <t>14,65; 22,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 8,19</t>
+          <t>1,75; 10,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-45,23; -35,46</t>
+          <t>-39,27; -29,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,87; 23,31</t>
+          <t>16,35; 24,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,38; 11,13</t>
+          <t>-1,32; 7,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-40,55; -31,04</t>
+          <t>-43,16; -34,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,88; 22,27</t>
+          <t>16,89; 22,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,94</t>
+          <t>1,89; 8,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-41,14; -34,49</t>
+          <t>-39,89; -33,42</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>27,71%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-50,8%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>29,07%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-57,39%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>27,71%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-52,14%</t>
+          <t>-55,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-54,61%</t>
+          <t>-53,07%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>23,23; 37,78</t>
+          <t>20,51; 34,68</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 12,21</t>
+          <t>2,44; 16,38</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-63,6; -52,0</t>
+          <t>-56,01; -44,6</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,68; 35,26</t>
+          <t>22,77; 36,14</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,41; 16,93</t>
+          <t>-1,87; 11,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-57,48; -46,15</t>
+          <t>-60,25; -50,56</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,74; 33,12</t>
+          <t>23,7; 33,57</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,65; 11,78</t>
+          <t>2,68; 12,57</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-58,81; -50,76</t>
+          <t>-56,93; -49,51</t>
         </is>
       </c>
     </row>
